--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513857_FF2ºA12ºA22ºA12ºA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513857_FF2ºA12ºA22ºA12ºA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3589</v>
+        <v>5.7005</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3007</v>
+        <v>2.3658</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0582</v>
+        <v>3.3348</v>
       </c>
       <c r="G2" t="n">
         <v>3.4453</v>
@@ -610,13 +610,13 @@
         <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2767</v>
+        <v>1.6183</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6253</v>
+        <v>0.6904</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6514</v>
+        <v>0.928</v>
       </c>
       <c r="V2" t="n">
         <v>1.2211</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.936</v>
+        <v>3.7699</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3692</v>
+        <v>1.7301</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5668</v>
+        <v>2.0398</v>
       </c>
       <c r="G3" t="n">
         <v>1.7087</v>
@@ -688,13 +688,13 @@
         <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6306</v>
+        <v>0.2033</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2538</v>
+        <v>0.1071</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3768</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>2.4421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.385</v>
+        <v>3.4406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1226</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2624</v>
+        <v>2.5963</v>
       </c>
       <c r="G4" t="n">
         <v>2.1542</v>
@@ -766,13 +766,13 @@
         <v>1.3632</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0155</v>
+        <v>1.0401</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1827</v>
+        <v>0.539</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1672</v>
+        <v>0.5011</v>
       </c>
       <c r="V4" t="n">
         <v>0.0516</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6821</v>
+        <v>1.3453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1911</v>
+        <v>-0.1458</v>
       </c>
       <c r="F5" t="n">
         <v>1.491</v>
@@ -844,10 +844,10 @@
         <v>0.7789</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9303</v>
+        <v>0.5934</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8436</v>
+        <v>0.5067</v>
       </c>
       <c r="U5" t="n">
         <v>0.0867</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8204</v>
+        <v>1.2493</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4549</v>
+        <v>0.37</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2753</v>
+        <v>0.8793</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0682</v>
+        <v>1.3266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1524</v>
+        <v>-0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2206</v>
+        <v>1.4476</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.838</v>
+        <v>1.6344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3695</v>
+        <v>0.3131</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2074</v>
+        <v>1.3213</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2302</v>
+        <v>-0.3078</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2171</v>
+        <v>-0.4342</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0131</v>
+        <v>0.1263</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3895</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3895</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
         <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4991</v>
+        <v>0.3122</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7725</v>
+        <v>-0.096</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7266</v>
+        <v>0.4082</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7114</v>
+        <v>0.6079</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0287</v>
+        <v>0.6079</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7401</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3266</v>
+        <v>0.6079</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1211</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4476</v>
+        <v>0.6079</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6344</v>
+        <v>0.6079</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3131</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3213</v>
+        <v>0.6079</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3078</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4342</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1263</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2257</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4947</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6079</v>
+        <v>0.4684</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6079</v>
+        <v>-1.7971</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.2656</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6079</v>
+        <v>0.1598</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.5208</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6079</v>
+        <v>0.6806</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6079</v>
+        <v>-0.4561</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.6183</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6079</v>
+        <v>0.1621</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.6159</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0974</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5185</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.5881</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.1726</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0535</v>
+        <v>0.2888</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2955</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.349</v>
+        <v>1.0806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1598</v>
+        <v>-1.0682</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5208</v>
+        <v>0.1524</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6806</v>
+        <v>-1.2206</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4561</v>
+        <v>-0.838</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6183</v>
+        <v>0.3695</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1621</v>
+        <v>-1.2074</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6159</v>
+        <v>-0.2302</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0974</v>
+        <v>-0.2171</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5185</v>
+        <v>-0.0131</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1684</v>
+        <v>-0.3895</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1684</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1732</v>
+        <v>0.9675</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.671</v>
+        <v>0.4356</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8442</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4485</v>
+        <v>-0.1209</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4004</v>
+        <v>-0.878</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9519</v>
+        <v>0.7571</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3965</v>
@@ -1234,13 +1234,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8964</v>
+        <v>1.224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0064</v>
+        <v>0.5159</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9029</v>
+        <v>0.7081</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5590000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5331</v>
+        <v>-1.0091</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0576</v>
+        <v>-0.2792</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5907</v>
+        <v>-0.7298</v>
       </c>
       <c r="G11" t="n">
         <v>0.6342</v>
@@ -1312,13 +1312,13 @@
         <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1901</v>
+        <v>0.7141</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7817</v>
+        <v>0.4449</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4084</v>
+        <v>0.2692</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1626</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9968</v>
+        <v>-1.5322</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5633</v>
+        <v>-1.4604</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4335</v>
+        <v>-0.0718</v>
       </c>
       <c r="G12" t="n">
         <v>2.1638</v>
@@ -1390,13 +1390,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.3362</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1897</v>
+        <v>0.2926</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3181</v>
+        <v>0.0436</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5005</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4754</v>
+        <v>-2.0922</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0854</v>
+        <v>-2.4012</v>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>0.309</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-2.5809</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3145</v>
+        <v>-0.2971</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9512</v>
+        <v>-2.2838</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5907</v>
+        <v>-2.4954</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.254</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3367</v>
+        <v>-1.8719</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9540999999999999</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5685</v>
+        <v>0.3263</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3856</v>
+        <v>-0.4118</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.7526</v>
+        <v>0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9474</v>
+        <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4172</v>
+        <v>0.5734</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5473</v>
+        <v>0.2889</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1301</v>
+        <v>0.2845</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3311</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3311</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.78</v>
+        <v>-2.1764</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0611</v>
+        <v>-3.7863</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2812</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5809</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2971</v>
+        <v>0.3145</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2838</v>
+        <v>-0.9512</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4954</v>
+        <v>-1.5907</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.254</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8719</v>
+        <v>-1.3367</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3263</v>
+        <v>0.5685</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4118</v>
+        <v>0.3856</v>
       </c>
       <c r="P14" t="n">
+        <v>-1.7526</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.9474</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.1947</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.1947</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3895</v>
-      </c>
       <c r="S14" t="n">
-        <v>-0.1144</v>
+        <v>-0.1181</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.371</v>
+        <v>-0.2483</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2567</v>
+        <v>0.1301</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2795</v>
+        <v>0.3311</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2795</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.321400000000001</v>
+        <v>9.939900000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.2402</v>
+        <v>-5.621699999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>15.5617</v>
+        <v>15.5619</v>
       </c>
       <c r="G15" t="n">
         <v>7.802800000000001</v>
@@ -1606,7 +1606,7 @@
         <v>3.0189</v>
       </c>
       <c r="M15" t="n">
-        <v>4.0673</v>
+        <v>4.067299999999999</v>
       </c>
       <c r="N15" t="n">
         <v>5.6258</v>
@@ -1624,13 +1624,13 @@
         <v>10.7104</v>
       </c>
       <c r="S15" t="n">
-        <v>7.4339</v>
+        <v>8.0525</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6859</v>
+        <v>3.3042</v>
       </c>
       <c r="U15" t="n">
-        <v>4.7483</v>
+        <v>4.748199999999998</v>
       </c>
       <c r="V15" t="n">
         <v>-0.07309999999999961</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5143</v>
+        <v>2.7462</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1508</v>
+        <v>0.6912</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6651</v>
+        <v>2.055</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.6706</v>
+        <v>3.5738</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.2862</v>
+        <v>-0.9842</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6156</v>
+        <v>4.558</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.1182</v>
+        <v>2.567</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.5771</v>
+        <v>-1.2264</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4589</v>
+        <v>3.7934</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5525</v>
+        <v>1.0068</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2909</v>
+        <v>0.2422</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8433</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3368</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7635</v>
+        <v>-0.9776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6774</v>
+        <v>-0.4679</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0861</v>
+        <v>-0.5097</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6116</v>
+        <v>-0.4342</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8395</v>
+        <v>-0.4342</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3653</v>
+        <v>1.8627</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0065</v>
+        <v>0.1482</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3718</v>
+        <v>1.7145</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5738</v>
+        <v>-3.6706</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9842</v>
+        <v>-4.2862</v>
       </c>
       <c r="I17" t="n">
-        <v>4.558</v>
+        <v>0.6156</v>
       </c>
       <c r="J17" t="n">
-        <v>2.567</v>
+        <v>-3.1182</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2264</v>
+        <v>-4.5771</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7934</v>
+        <v>1.4589</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0068</v>
+        <v>-0.5525</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2422</v>
+        <v>0.2909</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7645999999999999</v>
+        <v>-0.8433</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5842000000000001</v>
+        <v>2.3368</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5579</v>
+        <v>2.5316</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3585</v>
+        <v>-0.4151</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1656</v>
+        <v>-0.3784</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1929</v>
+        <v>-0.0367</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4342</v>
+        <v>3.6116</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4342</v>
+        <v>3.8395</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6425</v>
+        <v>0.998</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3691</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0116</v>
+        <v>1.3671</v>
       </c>
       <c r="G18" t="n">
         <v>0.998</v>
@@ -1858,13 +1858,13 @@
         <v>2.3368</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5239</v>
+        <v>-1.1684</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6248</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8991</v>
+        <v>-0.5436</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.625</v>
+        <v>-0.8718</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3016</v>
+        <v>-0.9941</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3233</v>
+        <v>0.1223</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7069</v>
@@ -1936,13 +1936,13 @@
         <v>2.1421</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6629</v>
+        <v>0.1661</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5635</v>
+        <v>0.2677</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.1015</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3311</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1474</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5947</v>
+        <v>-0.4951</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5526</v>
+        <v>-0.4197</v>
       </c>
       <c r="G20" t="n">
         <v>1.1837</v>
@@ -2014,13 +2014,13 @@
         <v>0.9737</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7789</v>
+        <v>-0.5464</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7946</v>
+        <v>-0.6949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0157</v>
+        <v>0.1486</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5521</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8902</v>
+        <v>-1.6854</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6334</v>
+        <v>-2.5338</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7433</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4637</v>
@@ -2092,13 +2092,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0107</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.742</v>
+        <v>-0.6423</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2687</v>
+        <v>-0.1636</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0464</v>
+        <v>-1.7482</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9956</v>
+        <v>-3.7962</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9492</v>
+        <v>2.048</v>
       </c>
       <c r="G22" t="n">
         <v>-2.235</v>
@@ -2170,13 +2170,13 @@
         <v>0.9737</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.785</v>
+        <v>-0.4868</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7946</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.1084</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2068</v>
+        <v>-2.3946</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3705</v>
+        <v>-2.6695</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1637</v>
+        <v>0.275</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8929</v>
@@ -2248,13 +2248,13 @@
         <v>2.3368</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4823</v>
+        <v>-0.67</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0221</v>
+        <v>-0.3212</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4602</v>
+        <v>-0.3489</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6828</v>
+        <v>-2.7933</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9396</v>
+        <v>-2.2387</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7432</v>
+        <v>-0.5546</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1897</v>
@@ -2326,13 +2326,13 @@
         <v>1.3632</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6615</v>
+        <v>-0.772</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4485</v>
+        <v>-0.7476</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.213</v>
+        <v>-0.0245</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2211</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4949</v>
+        <v>-3.1913</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8031</v>
+        <v>-3.3048</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3082</v>
+        <v>0.1135</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3992</v>
@@ -2404,13 +2404,13 @@
         <v>1.7526</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7325</v>
+        <v>-0.4289</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.042</v>
+        <v>-0.5436</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3094</v>
+        <v>0.1147</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.321399999999999</v>
+        <v>-7.9925</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.5617</v>
+        <v>-15.5619</v>
       </c>
       <c r="F26" t="n">
-        <v>6.240400000000001</v>
+        <v>7.569400000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-7.8025</v>
@@ -2482,13 +2482,13 @@
         <v>16.5526</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.4339</v>
+        <v>-6.105</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.7481</v>
+        <v>-4.7483</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6858</v>
+        <v>-1.3568</v>
       </c>
       <c r="V26" t="n">
         <v>0.07309999999999972</v>
